--- a/src/nodes/HPC/compressor_stage_4_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_4_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00057295206843256186</v>
       </c>
       <c r="B2">
-        <v>0.00045587221945384574</v>
+        <v>0.00049827067251785519</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0011459041368651237</v>
       </c>
       <c r="B3">
-        <v>0.00076539188096734728</v>
+        <v>0.00082383299194746854</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0017188562052976857</v>
       </c>
       <c r="B4">
-        <v>0.0010423773812074204</v>
+        <v>0.0011131942568656851</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0022918082737302474</v>
       </c>
       <c r="B5">
-        <v>0.0012934703831937277</v>
+        <v>0.0013742566248427187</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.002864760342162809</v>
       </c>
       <c r="B6">
-        <v>0.0015215477084451244</v>
+        <v>0.0016104104437682043</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0034377124105953714</v>
       </c>
       <c r="B7">
-        <v>0.0017283477213786279</v>
+        <v>0.0018236869455658061</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0040106644790279334</v>
       </c>
       <c r="B8">
-        <v>0.0019149879344089924</v>
+        <v>0.0020153755982598724</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0045836165474604949</v>
       </c>
       <c r="B9">
-        <v>0.0020830382142630294</v>
+        <v>0.0021873154907177555</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0051565686158930564</v>
       </c>
       <c r="B10">
-        <v>0.0022341605368777434</v>
+        <v>0.0023414593382210173</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.005729520684325618</v>
       </c>
       <c r="B11">
-        <v>0.0023699329607188612</v>
+        <v>0.0024796647408650654</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.00630247275275818</v>
       </c>
       <c r="B12">
-        <v>0.0024912678584311713</v>
+        <v>0.0026029931041641041</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0068754248211907428</v>
       </c>
       <c r="B13">
-        <v>0.0025964987768469926</v>
+        <v>0.0027094161704936822</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0074483768896233035</v>
       </c>
       <c r="B14">
-        <v>0.0026846735969615234</v>
+        <v>0.0027977653039468423</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0080213289580558667</v>
       </c>
       <c r="B15">
-        <v>0.0027602763622339471</v>
+        <v>0.0028734000186252722</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.0085942810264884265</v>
       </c>
       <c r="B16">
-        <v>0.0028274188024453037</v>
+        <v>0.0029412350218594751</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.00916723309492099</v>
       </c>
       <c r="B17">
-        <v>0.00288328723020008</v>
+        <v>0.0029978776438865924</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.0097401851633535513</v>
       </c>
       <c r="B18">
-        <v>0.002924213156352733</v>
+        <v>0.0030389118293020004</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.010313137231786113</v>
       </c>
       <c r="B19">
-        <v>0.002950034301934152</v>
+        <v>0.0030641353572273817</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.010886089300218674</v>
       </c>
       <c r="B20">
-        <v>0.0029614649405193373</v>
+        <v>0.0030743994654159959</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.011459041368651236</v>
       </c>
       <c r="B21">
-        <v>0.002959219345683287</v>
+        <v>0.0030705553916211023</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.012031993437083798</v>
       </c>
       <c r="B22">
-        <v>0.0029438803171843793</v>
+        <v>0.0030532985278336239</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.012604945505516361</v>
       </c>
       <c r="B23">
-        <v>0.0029155047595145122</v>
+        <v>0.0030227008829951376</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.013177897573948922</v>
       </c>
       <c r="B24">
-        <v>0.0028740181033489625</v>
+        <v>0.002978678620284884</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.013750849642381486</v>
       </c>
       <c r="B25">
-        <v>0.002819345779363006</v>
+        <v>0.002921147902882104</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.014323801710814045</v>
       </c>
       <c r="B26">
-        <v>0.0027513835139329991</v>
+        <v>0.0028499911861637611</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.014896753779246607</v>
       </c>
       <c r="B27">
-        <v>0.0026699082162396043</v>
+        <v>0.002764956094297714</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.01546970584767917</v>
       </c>
       <c r="B28">
-        <v>0.0025746670911645643</v>
+        <v>0.0026657565436495451</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.016042657916111733</v>
       </c>
       <c r="B29">
-        <v>0.0024654073435896214</v>
+        <v>0.0025521064505848365</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.016615609984544293</v>
       </c>
       <c r="B30">
-        <v>0.0023419559953507412</v>
+        <v>0.0024238177324898747</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.017188562052976853</v>
       </c>
       <c r="B31">
-        <v>0.0022044593361007828</v>
+        <v>0.0022810943108337585</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.017761514121409416</v>
       </c>
       <c r="B32">
-        <v>0.0020531434724468276</v>
+        <v>0.0021242381081062892</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.01833446618984198</v>
       </c>
       <c r="B33">
-        <v>0.0018882345109959581</v>
+        <v>0.0019535510467972705</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.018907418258274539</v>
       </c>
       <c r="B34">
-        <v>0.0017097972153545065</v>
+        <v>0.0017691443640878925</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.019480370326707103</v>
       </c>
       <c r="B35">
-        <v>0.0015172509771258012</v>
+        <v>0.0015703665559248974</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.020053322395139662</v>
       </c>
       <c r="B36">
-        <v>0.0013098538449124221</v>
+        <v>0.0013563754329464176</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.020626274463572226</v>
       </c>
       <c r="B37">
-        <v>0.0010868638673169459</v>
+        <v>0.0011263288057905808</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.021199226532004789</v>
       </c>
       <c r="B38">
-        <v>0.00084716196051748806</v>
+        <v>0.00087893536840557662</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.021772178600437349</v>
       </c>
       <c r="B39">
-        <v>0.00058812051099431156</v>
+        <v>0.00061110734797982578</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.022345130668869912</v>
       </c>
       <c r="B40">
-        <v>0.00030673477280321527</v>
+        <v>0.00031930785501180697</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.022918082737302472</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>7.95130722975548E-20</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.022345130668869912</v>
       </c>
       <c r="B43">
-        <v>0.00018100395071729859</v>
+        <v>0.00016843086850870691</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.021772178600437349</v>
       </c>
       <c r="B44">
-        <v>0.00035825214113916821</v>
+        <v>0.00033526530415365388</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.021199226532004789</v>
       </c>
       <c r="B45">
-        <v>0.00052942788163660287</v>
+        <v>0.00049765447374851431</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.020626274463572226</v>
       </c>
       <c r="B46">
-        <v>0.00069221448258059725</v>
+        <v>0.00065274954410696239</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.020053322395139662</v>
       </c>
       <c r="B47">
-        <v>0.0008446379645724708</v>
+        <v>0.0007981163765384755</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.019480370326707103</v>
       </c>
       <c r="B48">
-        <v>0.00098609518913484015</v>
+        <v>0.000932979610335744</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.018907418258274539</v>
       </c>
       <c r="B49">
-        <v>0.0011163257280206488</v>
+        <v>0.0010569785792872628</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.01833446618984198</v>
       </c>
       <c r="B50">
-        <v>0.0012350691529828377</v>
+        <v>0.0011697526171815255</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.017761514121409416</v>
       </c>
       <c r="B51">
-        <v>0.0013421971158522122</v>
+        <v>0.0012711024801927507</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.017188562052976853</v>
       </c>
       <c r="B52">
-        <v>0.001438109588771029</v>
+        <v>0.0013614746140380536</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.016615609984544293</v>
       </c>
       <c r="B53">
-        <v>0.001523338623959408</v>
+        <v>0.0014414768868202747</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.016042657916111733</v>
       </c>
       <c r="B54">
-        <v>0.0015984162736374693</v>
+        <v>0.0015117171666422541</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.01546970584767917</v>
       </c>
       <c r="B55">
-        <v>0.0016637725663147562</v>
+        <v>0.0015726831138297755</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.014896753779246607</v>
       </c>
       <c r="B56">
-        <v>0.0017194294356585053</v>
+        <v>0.0016243815576003956</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.014323801710814045</v>
       </c>
       <c r="B57">
-        <v>0.0017653067916253765</v>
+        <v>0.0016666991193946144</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.013750849642381486</v>
       </c>
       <c r="B58">
-        <v>0.0018013245441720303</v>
+        <v>0.001699522420652933</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.013177897573948922</v>
       </c>
       <c r="B59">
-        <v>0.0018274129339897432</v>
+        <v>0.0017227524170538215</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.012604945505516361</v>
       </c>
       <c r="B60">
-        <v>0.0018435435247082584</v>
+        <v>0.0017363474012276334</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.012031993437083798</v>
       </c>
       <c r="B61">
-        <v>0.0018496982106919351</v>
+        <v>0.001740280000042691</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.011459041368651236</v>
       </c>
       <c r="B62">
-        <v>0.0018458588863051325</v>
+        <v>0.0017345228403673175</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.010886089300218674</v>
       </c>
       <c r="B63">
-        <v>0.0018321196915527518</v>
+        <v>0.0017191851666560933</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.010313137231786113</v>
       </c>
       <c r="B64">
-        <v>0.0018090237490018576</v>
+        <v>0.0016949226937086283</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.0097401851633535513</v>
       </c>
       <c r="B65">
-        <v>0.0017772264268600571</v>
+        <v>0.0016625277539107895</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.00916723309492099</v>
       </c>
       <c r="B66">
-        <v>0.0017373830933349566</v>
+        <v>0.0016227926796484442</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.0085942810264884265</v>
       </c>
       <c r="B67">
-        <v>0.0016892566083035897</v>
+        <v>0.0015754403888894181</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0080213289580558667</v>
       </c>
       <c r="B68">
-        <v>0.0016290397983206968</v>
+        <v>0.0015159161419293719</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0074483768896233035</v>
       </c>
       <c r="B69">
-        <v>0.001553756527108333</v>
+        <v>0.0014406648201230141</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0068754248211907428</v>
       </c>
       <c r="B70">
-        <v>0.0014673248403800998</v>
+        <v>0.0013544074467334104</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.00630247275275818</v>
       </c>
       <c r="B71">
-        <v>0.00137401540110184</v>
+        <v>0.0012622901553689069</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.005729520684325618</v>
       </c>
       <c r="B72">
-        <v>0.0012726151592568188</v>
+        <v>0.0011628833791106146</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0051565686158930564</v>
       </c>
       <c r="B73">
-        <v>0.0011611725234450053</v>
+        <v>0.0010538737221017316</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0045836165474604949</v>
       </c>
       <c r="B74">
-        <v>0.0010402654497157664</v>
+        <v>0.00093598817326104029</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0040106644790279334</v>
       </c>
       <c r="B75">
-        <v>0.00091111129590018948</v>
+        <v>0.00081072363204930922</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0034377124105953714</v>
       </c>
       <c r="B76">
-        <v>0.00077495547950684506</v>
+        <v>0.00067961625531966674</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.002864760342162809</v>
       </c>
       <c r="B77">
-        <v>0.000632920355214324</v>
+        <v>0.000544057619891244</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0022918082737302474</v>
       </c>
       <c r="B78">
-        <v>0.00048560796670381551</v>
+        <v>0.00040482172505482437</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0017188562052976857</v>
       </c>
       <c r="B79">
-        <v>0.00033420862462477384</v>
+        <v>0.00026339174896650928</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0011459041368651237</v>
       </c>
       <c r="B80">
-        <v>0.00018098077116613439</v>
+        <v>0.00012253966018601313</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00057295206843256186</v>
       </c>
       <c r="B81">
-        <v>3.1887688813749977E-05</v>
+        <v>-1.0510764250259578E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00062144362209978884</v>
       </c>
       <c r="B2">
-        <v>0.00058255573205030287</v>
+        <v>0.00067452938812107152</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0012428872441995777</v>
       </c>
       <c r="B3">
-        <v>0.0009494944131437854</v>
+        <v>0.0010762689120521424</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0018643308662993666</v>
       </c>
       <c r="B4">
-        <v>0.0012734669502746381</v>
+        <v>0.0014270878136577057</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0024857744883991554</v>
       </c>
       <c r="B5">
-        <v>0.0015643948376378239</v>
+        <v>0.001739641939069964</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0031072181104989439</v>
       </c>
       <c r="B6">
-        <v>0.0018264975225135876</v>
+        <v>0.0020192647124809612</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0037286617325987333</v>
       </c>
       <c r="B7">
-        <v>0.0020622830005410748</v>
+        <v>0.0022690994379758844</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0043501053546985222</v>
       </c>
       <c r="B8">
-        <v>0.0022733244851097728</v>
+        <v>0.0024910923469425991</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0049715489767983108</v>
       </c>
       <c r="B9">
-        <v>0.0024618986640769151</v>
+        <v>0.0026881041425212381</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0055929925988980993</v>
       </c>
       <c r="B10">
-        <v>0.00263042961671131</v>
+        <v>0.0028631895958702936</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0062144362209978878</v>
       </c>
       <c r="B11">
-        <v>0.0027812275134603322</v>
+        <v>0.0030192652784694352</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.0068358798430976772</v>
       </c>
       <c r="B12">
-        <v>0.0029155980331892657</v>
+        <v>0.0031579601615893144</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0074573234651974666</v>
       </c>
       <c r="B13">
-        <v>0.0030309427972564692</v>
+        <v>0.0032758910153433216</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.0080787670872972551</v>
       </c>
       <c r="B14">
-        <v>0.0031257539432842734</v>
+        <v>0.0033710802939183561</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0087002107093970445</v>
       </c>
       <c r="B15">
-        <v>0.0032067897314578364</v>
+        <v>0.0034521853889526014</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.0093216543314968321</v>
       </c>
       <c r="B16">
-        <v>0.0032802477748009578</v>
+        <v>0.0035271457878928579</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.0099430979535966215</v>
       </c>
       <c r="B17">
-        <v>0.0033418169751291828</v>
+        <v>0.0035903944239690979</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.010564541575696411</v>
       </c>
       <c r="B18">
-        <v>0.0033858938787017382</v>
+        <v>0.0036347061710201188</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.011185985197796199</v>
       </c>
       <c r="B19">
-        <v>0.0034122143207608278</v>
+        <v>0.0036597302195368474</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.011807428819895988</v>
       </c>
       <c r="B20">
-        <v>0.0034218489587944005</v>
+        <v>0.0036668343391732436</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.012428872441995776</v>
       </c>
       <c r="B21">
-        <v>0.0034158684502904051</v>
+        <v>0.0036573862995832665</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.013050316064095565</v>
       </c>
       <c r="B22">
-        <v>0.0033951483671579553</v>
+        <v>0.00363250591553217</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.013671759686195354</v>
       </c>
       <c r="B23">
-        <v>0.0033597839389908281</v>
+        <v>0.0035923211822303891</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.014293203308295144</v>
       </c>
       <c r="B24">
-        <v>0.0033096753098039665</v>
+        <v>0.0035367121399996529</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.014914646930394933</v>
       </c>
       <c r="B25">
-        <v>0.0032447226236123118</v>
+        <v>0.0034655588291616921</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.015536090552494719</v>
       </c>
       <c r="B26">
-        <v>0.0031647855211046957</v>
+        <v>0.0033786921020358238</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.01615753417459451</v>
       </c>
       <c r="B27">
-        <v>0.0030695616296655013</v>
+        <v>0.0032757460589317097</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.016778977796694298</v>
       </c>
       <c r="B28">
-        <v>0.0029587080733530003</v>
+        <v>0.0031563056121566</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.017400421418794089</v>
       </c>
       <c r="B29">
-        <v>0.0028318819762254643</v>
+        <v>0.0030199556740177439</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.018021865040893877</v>
       </c>
       <c r="B30">
-        <v>0.0026888669754540871</v>
+        <v>0.0028664471160696776</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.018643308662993664</v>
       </c>
       <c r="B31">
-        <v>0.0025299527606617513</v>
+        <v>0.002696194646856082</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.019264752285093452</v>
       </c>
       <c r="B32">
-        <v>0.0023555555345842593</v>
+        <v>0.0025097789341679225</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.019886195907193243</v>
       </c>
       <c r="B33">
-        <v>0.0021660914999574155</v>
+        <v>0.0023077806457961676</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.020507639529293031</v>
       </c>
       <c r="B34">
-        <v>0.0019617389518417792</v>
+        <v>0.0020904788904934231</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.021129083151392822</v>
       </c>
       <c r="B35">
-        <v>0.0017417245545969331</v>
+        <v>0.0018569465408588509</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.021750526773492606</v>
       </c>
       <c r="B36">
-        <v>0.0015050370649072168</v>
+        <v>0.0016059549104532546</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.022371970395592397</v>
       </c>
       <c r="B37">
-        <v>0.0012506652394569664</v>
+        <v>0.0013362753128374333</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.022993414017692185</v>
       </c>
       <c r="B38">
-        <v>0.00097703362065337481</v>
+        <v>0.0010459586940489405</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.023614857639791976</v>
       </c>
       <c r="B39">
-        <v>0.00068030989379504517</v>
+        <v>0.00073017453003233214</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.024236301261891764</v>
       </c>
       <c r="B40">
-        <v>0.00035609752990343406</v>
+        <v>0.00038337192920891573</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.024857744883991551</v>
       </c>
       <c r="B41">
-        <v>-8.6242627220205034E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.024236301261891764</v>
       </c>
       <c r="B43">
-        <v>0.00016517673476506379</v>
+        <v>0.00013790233545958223</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.023614857639791976</v>
       </c>
       <c r="B44">
-        <v>0.00033125744013403642</v>
+        <v>0.00028139280389674945</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.022993414017692185</v>
       </c>
       <c r="B45">
-        <v>0.00049455810688441514</v>
+        <v>0.00042563303348884957</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.022371970395592397</v>
       </c>
       <c r="B46">
-        <v>0.00065139472579369806</v>
+        <v>0.00056578465241323124</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.021750526773492606</v>
       </c>
       <c r="B47">
-        <v>0.00079861214608495054</v>
+        <v>0.00069769430053891256</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.021129083151392822</v>
       </c>
       <c r="B48">
-        <v>0.00093517065076350778</v>
+        <v>0.00081994866450158985</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.020507639529293031</v>
       </c>
       <c r="B49">
-        <v>0.0010605593812802743</v>
+        <v>0.00093181944262863065</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.019886195907193243</v>
       </c>
       <c r="B50">
-        <v>0.0011742674790861528</v>
+        <v>0.0010325783332474007</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.019264752285093452</v>
       </c>
       <c r="B51">
-        <v>0.001275991737498619</v>
+        <v>0.0011217683379149562</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.018643308662993664</v>
       </c>
       <c r="B52">
-        <v>0.0013662595573014401</v>
+        <v>0.0012000176711071098</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.018021865040893877</v>
       </c>
       <c r="B53">
-        <v>0.0014458059911449548</v>
+        <v>0.0012682258505293648</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.017400421418794089</v>
       </c>
       <c r="B54">
-        <v>0.0015153660916795038</v>
+        <v>0.0013272923938872239</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.016778977796694298</v>
       </c>
       <c r="B55">
-        <v>0.0015755253017277976</v>
+        <v>0.0013779277629241977</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.01615753417459451</v>
       </c>
       <c r="B56">
-        <v>0.0016262706248020378</v>
+        <v>0.0014200861955358287</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.015536090552494719</v>
       </c>
       <c r="B57">
-        <v>0.0016674394545867959</v>
+        <v>0.0014535328736556673</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.014914646930394933</v>
       </c>
       <c r="B58">
-        <v>0.0016988691847666451</v>
+        <v>0.0014780329792172639</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.014293203308295144</v>
       </c>
       <c r="B59">
-        <v>0.0017204174984341574</v>
+        <v>0.0014933806682384703</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.013671759686195354</v>
       </c>
       <c r="B60">
-        <v>0.0017320232363139028</v>
+        <v>0.0014994859930743422</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.013050316064095565</v>
       </c>
       <c r="B61">
-        <v>0.0017336455285384511</v>
+        <v>0.0014962879801642362</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.012428872441995776</v>
       </c>
       <c r="B62">
-        <v>0.0017252435052403715</v>
+        <v>0.0014837256559475098</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.011807428819895988</v>
       </c>
       <c r="B63">
-        <v>0.0017069512961424933</v>
+        <v>0.0014619659157636498</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.011185985197796199</v>
       </c>
       <c r="B64">
-        <v>0.0016796030293286834</v>
+        <v>0.0014320871305526632</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.010564541575696411</v>
       </c>
       <c r="B65">
-        <v>0.0016442078324730681</v>
+        <v>0.0013953955401546871</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.0099430979535966215</v>
       </c>
       <c r="B66">
-        <v>0.0016017748332497739</v>
+        <v>0.0013531973844098585</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.0093216543314968321</v>
       </c>
       <c r="B67">
-        <v>0.0015519616831576558</v>
+        <v>0.0013050636700657557</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0087002107093970445</v>
       </c>
       <c r="B68">
-        <v>0.0014890201289944843</v>
+        <v>0.0012436244714997197</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.0080787670872972551</v>
       </c>
       <c r="B69">
-        <v>0.0014084694888456986</v>
+        <v>0.0011631431382116166</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0074573234651974666</v>
       </c>
       <c r="B70">
-        <v>0.0013163052706485</v>
+        <v>0.0010713570525616473</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.0068358798430976772</v>
       </c>
       <c r="B71">
-        <v>0.0012190631343889278</v>
+        <v>0.00097670100598887949</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0062144362209978878</v>
       </c>
       <c r="B72">
-        <v>0.0011149631583966108</v>
+        <v>0.000876925393387508</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0055929925988980993</v>
       </c>
       <c r="B73">
-        <v>0.0010011097625984265</v>
+        <v>0.0007683497834394433</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0049715489767983108</v>
       </c>
       <c r="B74">
-        <v>0.0008784603149666532</v>
+        <v>0.00065225483652233014</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0043501053546985222</v>
       </c>
       <c r="B75">
-        <v>0.0007489494522799888</v>
+        <v>0.00053118159044716266</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0037286617325987333</v>
       </c>
       <c r="B76">
-        <v>0.00061456793849740642</v>
+        <v>0.00040775150106259683</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0031072181104989439</v>
       </c>
       <c r="B77">
-        <v>0.00047712719274197081</v>
+        <v>0.00028436000277459712</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0024857744883991554</v>
       </c>
       <c r="B78">
-        <v>0.00033766512761284083</v>
+        <v>0.00016241802618070057</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0018643308662993666</v>
       </c>
       <c r="B79">
-        <v>0.00019812090659316321</v>
+        <v>4.4500043210095533E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0012428872441995777</v>
       </c>
       <c r="B80">
-        <v>6.2072920785287181E-05</v>
+        <v>-6.4701578123069656E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00062144362209978884</v>
       </c>
       <c r="B81">
-        <v>-6.1259860445078378E-05</v>
+        <v>-0.00015323351651584704</v>
       </c>
     </row>
     <row r="82" spans="1:2">
